--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.323652367119357</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.045391527294317</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.246672130740395</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.000408310172124023</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.009471640885287e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>72.22095309270408</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29.71600450506989</v>
+      </c>
+      <c r="M13" t="n">
+        <v>63.64967045349237</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001632297988474344</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.000160527487017003</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003165106502925526</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001643401707432937</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0009133330975553768</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001168262357168715</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0007930354694872657</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.418436301599731e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.424029163614708e-06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.129812324779149e-05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0001363697953517355</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.637077572453192e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.373035763801288e-05</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.371767091143083e-05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0001330848694122446</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0009143362326634966</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0002179037246182904</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0001659383952935523</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.891843952394212e-05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0009229961821670845</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.00106527710371059</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0004253484688661774</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0001913948626254639</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0001335833775913147</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0007885664145268948</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.002517070711898365</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.001152966650121953</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.005125183988656061</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.002554227597976307</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.02660446885174964</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.003270755862036623</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.002428690285628675</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9.995371012353852e-06</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.573180211488261e-06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.511664120501515e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0002159580732078818</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.325097102778911e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.614079476465231e-05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.731406531629396e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0005058382489048185</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0008080570217051294</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0002338532459197281</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0005119249477790374</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0004662987863654515</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.002243039876845437</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.005325357488914051</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.003842303258443233</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0001365276112809492</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0001138947341075776</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.002252430283169741</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.01158204209567278</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.001404750546062043</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0004443656364676862</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0001427790640705659</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2368141097428768</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.134208645516386</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.05916191390023432</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.378710525886902e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.775467560446079e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000211745044488701</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01136710321776491</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001404665429537264</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.399728247428253e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.132928984604966e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002677422741729363</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0005106216369388979</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0001041337192725743</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0006392510454019303</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002554520660919807</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001891104552163669</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001417818422567052</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003839616320127029</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.916197634567524e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.038654231867196e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0008902357287412642</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.00149520446399265</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0003615130852660129</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.765060483685896e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.969606582619997e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002992738834194712</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001072323765280695</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.000470664326584901</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001737735229223603</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.581941008583314e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0007159450587435821</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001685011769723133</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006755095013870097</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002633806266743329</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0007969936256878496</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.007987823897709205</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00202866208485375</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0008834847032077162</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001913948626254639</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001335833775913147</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0007885664145268948</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002517070711898365</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001152966650121953</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003832289571838269</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002088977449531033</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001172625324757767</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002558219726912133</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.001539190003321973</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0006798121418552702</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0003630398022401181</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.002805781527428344</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002694400740561302</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001833956925304374</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0006053171172486493</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002452648508174174</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001515890652492814</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003324514182367011</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001557698468968002</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.029930450823784e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.337716162281787e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001401941321855331</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0006582758197168914</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.939972630713045e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0002066291170423895</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001323602929363131</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0008565778267571983</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001945503760680367</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001082829463258312</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001700450276295543</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001314710283071707</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0006958295505323832</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001926793644467277</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.00111111045690733</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001922301302017537</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001310285922643718</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0007538238022973112</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002142129012592401</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001118414299433647</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003400169503248544</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000182623239341165</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.002310843657024677</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002141318512409877</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001120741644410529</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002166658696815353</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.000147138905421054</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0009889126277424509</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002530937364402538</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.00115193617839194</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001913948626254639</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001335833775913147</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0007885664145268948</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002517070711898365</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001152966650121953</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001765099586862699</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001348408178628042</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0007138264911166751</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002508899272546235</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001152922833664084</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001936716884514874</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001316914844142758</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0008949876382760808</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002503500580398092</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001152559332776133</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001119021470032955</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001021198026527432</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0003013828244502025</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02584115973180208</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01137404281744854</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001247864073075089</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001072234659495083</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0003808994610007001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01270262888526001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006206111964660459</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001068879280120931</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001071119400232269</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0003333282284910098</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00299309687678336</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002113248148080531</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001272898545854328</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000108252132109314</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000447856974532877</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002484382353410789</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001619906529215438</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.000314625389068605</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001757934760888854</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.002067258629000053</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002477161073140147</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001239775558268564</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.000518502576655866</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0002480621816031717</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.00317192408573502</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002498173643933418</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001193862330940033</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001825968039255166</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001332355739819841</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0007075072181450021</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002514972368051834</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.00115748919369749</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001913948626254639</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001335833775913147</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0007885664145268948</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002517070711898365</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001152966650121953</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0002045403277667705</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001338613408913699</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0008344706111109879</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002518759566820942</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.001149352519680257</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0002041710040419827</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0001343273801521392</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0008579761019338588</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002518965683634633</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001148901092634371</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001976281799772236</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001359347181237035</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0009237498816536126</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002519135634997838</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001148539863527685</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001960965809725638</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001363286029500466</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0009373313058830084</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002519150599293122</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.001148494734119052</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001945810474441127</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001366764897342979</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0009489868170590315</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002519171768274949</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.001148458596730177</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001874722250265748</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001230185687998474</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0006181676414770524</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002625537376726849</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006280932936145027</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001141252030568696</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0002659624099685688</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001876887695988464</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.00189201023484283</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003474133123703626</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.00617173752418639</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0005997232534768834</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.004477655874557607</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00191832144578874</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002033561663792</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.003437862492367957</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004703222034670077</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.004091145832327218</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001931438334907609</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001448704347341567</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001913948626254639</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001335833775913147</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0007885664145268948</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002517070711898365</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001152966650121953</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001988008966020693</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001410456759703986</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001606348098897724</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001773555932412648</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001449650085757322</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0007074384551838028</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001715506429471328</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.002416199168523895</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001543694460491111</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.002034825898444723</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001989850561094908</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001276456220194945</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.000763568624095969</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001852342745543615</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003475494773270031</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001874791063315821</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001230201195627369</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0006182025992837805</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002625537390634539</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.006280932953978786</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BB390C-D55B-45B0-BB77-559CE1428CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.125135369564124e-06</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.370531256470544e-06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.201398437682434e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.000145859556596406</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.608115794419801e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.200284050549248e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.524416328589995e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001071586678248148</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.000581187982030921</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.052143740965951e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.389532721624159e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.227558470620201e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000149092730282331</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0002422704455208683</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002531044712473995</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001807498248527217</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001816781518665136</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0007961737240103524</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001792121302363133</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001519918395991816</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.754281457819721e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.571684246681933e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.04312982806131e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0002470079123971421</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.864089456430656e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.243825756102306e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.48623207570031e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.625619848102035e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0005638646994915083</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.221173957323232e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.489546558570588e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.365259237593495e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.00012056789411212</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001058684775554486</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001648598964137264</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.657598469208878e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.879115597467348e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001991099565661162</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009286866406531166</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002705349848432084</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.320002604143227e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.961352977942951e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002726993898029764</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001734731731332317</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005620181557737671</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0002235561198786762</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002174420725396398</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.000912799889899016</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003346339044734729</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001903736751277484</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.981537082365742e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.309037379106344e-06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.005511274174773603</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.06500011445799221</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001860503815130024</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001572849829927966</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.364583706467225e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.02302489474877154</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5642431650776416</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01322887367942884</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0004464222838932071</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0004068458793173107</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.02288985094868308</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13.96369765741595</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2802373817014405</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.004795918714537291</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.004469842706544731</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.06601726228256664</v>
+      </c>
+      <c r="N15" t="n">
+        <v>94.44132230403677</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.850225923542911</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1316068818056742</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1244198961132828</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5047389596931621</v>
+      </c>
+      <c r="N16" t="n">
+        <v>153.2702828897915</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.368991991351906</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1272851819930252</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01347050118064698</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1976153407710673</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03486522923378743</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004242649317559484</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.613557715374792e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.363819430639703e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001386083197660205</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.00185980761019285</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004242089424293357</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001225194246640508</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.829596040945838e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0007956452025613416</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001929704135667028</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0008156773983648777</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002200946090866</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001798441195276147</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001526086181015933</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003879636123353218</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001624326041618</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001529949167085339</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0006038705401794138</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.006781183220008637</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.004599152029849544</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002351351724788178</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0005901210398662945</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004299526209586325</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.002993857477048615</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.005276113752339977</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003172834337816744</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.005501995853670838</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.002402743194552506</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03560907392782738</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.005776097101062305</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.004222982146691827</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004758991494991187</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002012380743370383</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.004417121955745948</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003101598324557623</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003677630411963949</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.058419062343312e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.516888702480328e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.589733757694678e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0003923812428562694</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.447691932042026e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.772001878608265e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.15809682061007e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.770019741987444e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.000488101417706351</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.000101749974260467</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0005357384391088497</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001597138697944885</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001143197703910226</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.000588556874712746</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0001664097442673545</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.998551837027577e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.222064277803104e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0002171367918918413</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0006946005290160429</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.00021962528691223</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001474633666368833</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.354227300430304e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0003949757071594096</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001088790694817969</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0003603704798853554</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0001974698197573233</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.991804947448899e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0005732381948551882</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.001483976387049779</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0006009003185865232</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.024957799614464e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.944489791192932e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002487610574393254</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.000895228325437832</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0005239190073342115</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.023323500666441e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.942451955871898e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002484720839884854</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008952776796225711</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0005238208524765465</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.022229977794188e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.940150675592936e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002483443014743395</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.000895345617360969</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0005235476434583271</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.021452820048623e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.938813157730423e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002483246299670979</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0008953837674804769</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005233525350150848</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.023907771594376e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.94182656010965e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.000248494604223923</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0008954458042656673</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.000523453133894399</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.498833222560545e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.077742075959597e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003001111259412224</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001735847091763295</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005620064353766008</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.423345867142179e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.056995658670238e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002842785555061911</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001735152736825303</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005621659470993285</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.320002604143227e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.961352977942951e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002726993898029764</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001734731731332317</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005620181557737671</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.920136922205205e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.557203197236383e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0006840556383136809</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00198295549737774</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005647631178973059</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.514099277563304e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.491346123373098e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0003734810553555163</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001981218701966251</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005648607623257018</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.599797745467408e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.866639645220429e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001472341004022424</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02695398966413147</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.006480086727439775</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.517009541723146e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.633059890095921e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002441413083133489</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01346901427617316</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003413478696455146</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.64826837001849e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.984137724228836e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001577144050806364</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002682091391231249</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.00103026109911382</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.424317606831745e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.044453624142251e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000421342697104866</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001849473578128406</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0007698806029767006</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.815138275977461e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.317627545795182e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0004263948049251321</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001705820132206289</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005954459236510779</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.00010732232965364</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.107051769242552e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.002064719303960807</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001721036408014243</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005773537805416379</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.967275951620129e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.680907980704784e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002905209007165966</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001733209835540113</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005636754569191684</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.320002604143227e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.961352977942951e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002726993898029764</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001734731731332317</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005620181557737671</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001580289809406388</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.418183143063503e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001156375949602782</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001735948902400253</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005607011988441008</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001126949445861373</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.633257378700615e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0007269916465971479</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001736100804509514</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005605373793491492</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.000111550422936979</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.38432346708619e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.000550003794523985</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001736222950834569</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0005604059379495999</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001128784748947176</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.371975433692058e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0005354371369180708</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001736238043257288</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0005603895189090001</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001142537829694016</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.365345097009237e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0005247111237519802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001736250174005249</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0005603765417061434</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.116591937085838e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.298549112219268e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001400504645267732</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00269691534079963</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.00372880063794393</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.19424600056077e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.544448057776008e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001731941013855993</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002443521858260874</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001859617918914095</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.041036719461029e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.160467285257716e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001355091470252221</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001970869871948352</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001004441508735394</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.350618042276028e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.944893850171948e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001606651954942626</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001651653861414859</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0006936167536690971</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.320002604143227e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.961352977942951e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002726993898029764</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001734731731332317</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005620181557737671</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.528697939023331e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.939282642459413e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0005675485322381363</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001253782612990658</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0006845631367334607</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.144114103504091e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.350970062734444e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003784561449324562</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00125218829252242</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0009866775270629788</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.89223403991331e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.537785165055757e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002753452691090789</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001939768016069691</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001830932391350949</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.116592630353504e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.298549092179459e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001400505127117656</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002696915347924005</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003728800675279989</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>444.543526934468</v>
+      </c>
+      <c r="L2" t="n">
+        <v>294.9478073364938</v>
+      </c>
+      <c r="M2" t="n">
+        <v>70742.24773331892</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6716583559558379</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.000484133201483</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>113.6901764498642</v>
+      </c>
+      <c r="L3" t="n">
+        <v>74.49023497311234</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17883.60222395913</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.686633423947976</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.010482613545442</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.913961352065305e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.486361757494146e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.426851933578063e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.744067880181926e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.911481971317333e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.888088135426074e-07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.443934750306593e-07</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.464490886726216e-06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.208414899650961e-06</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7.250235579898863e-06</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.628776097805655e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.803996718437875e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.792137040465217e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.907173849413084e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.78790562081285e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.606087190057319e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.599973791024646e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.571034879629479e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0001705654940830451</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001367827800907252</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.222667644727414e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.159696234668379e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001298304153336299</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0003455506115794075</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0002708935722351184</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.820928751617179e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.650730959796562e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002322637715500182</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006278914814477806</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004853719179328397</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.798120380984561e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.447518637149318e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.000388419769246487</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001061217333851043</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0008125427371095701</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0002345562952091503</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002243345411579462</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0009226250049645932</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002552802694973858</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001932323833297496</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0011650513579838</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.001105076213783466</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.004547039237664285</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.01273297872360975</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.009526468609192177</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.003666112949025339</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.003466926278785257</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01426944726449437</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.04003590317415728</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02982941627433506</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0187661069954328</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01770323655906162</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.07287128957488911</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.201911342864643</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.1499871158878298</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06195695772515612</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.05835464392723997</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2399157987609462</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.637206123719011</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4728414673052375</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4335792770264265</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4063538938197873</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.652308099159241</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.221321249460857</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.388592625640255</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,4 +2094,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.798120380984561e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.447518637149318e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000388419769246487</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001061217333851043</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0008125427371095701</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.81160193817369e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.461960324523993e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0003889960139812626</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001062142480236616</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0008136869635669523</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002258135979911202</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002154555353647443</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0008910409294142293</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002446194373381635</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001855777567302484</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0006129585474229001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000460907970934736</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.00211576193263087</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005235683861731862</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.003841730528642714</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002092499738314268</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.000780608913681975</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.007644627529008425</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.006763939672964625</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.004610374219601161</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001187371341338543</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0008058039091106203</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01467684957248144</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01044969827974758</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.006722463112948214</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.04208906794795181</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.01475530442342919</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2069243535849879</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01803323093918152</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.009826047525008217</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.004658980370389809</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002566455317213989</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02590010186006214</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02347714061518976</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01317197077901257</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01960168953607855</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.005701694219087694</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06432179286161624</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03594371054350631</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01618407364001871</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2690,4 +2691,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.798120380984561e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.447518637149318e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000388419769246487</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001061217333851043</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0008125427371095701</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.8167887993957e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.46522594062908e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0003891479056666685</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001063292298795204</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0008140691374199482</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.808223312335329e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.455255346205253e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0003887425203415831</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001062446978039588</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0008132550159663029</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.799282751895196e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.448574280563601e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0003884628551759708</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001061335716106744</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0008126312358146722</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.787749585502918e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.437670710005633e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0003880144666511561</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001060078933846853</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0008116921064329843</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.78783969197335e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.437724390967831e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003880165477248575</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001060097699678408</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0008116947765605939</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.790699228743686e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.440455080896947e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003881288085090605</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001060364401458476</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0008119300438433107</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.7960542338645e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.445569045927252e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003883393891671931</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001060994165148562</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.000812375052472844</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.784700044631241e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.435287851585073e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0003879149476731968</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001059733329232889</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0008114718614280179</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.77482479207481e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.426907956150211e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.000387567615360245</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001058633046075859</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0008107212077765996</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3342,4 +3343,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.733291863669777e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.708046927893597e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001956214386251277</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01123279177894195</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.008349703117403271</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.69907871069982e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.649066923878735e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001995422115785077</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.006146496006598075</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.004580569456184977</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.092747088891886e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.810896318790402e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002343322444887774</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00207745893082271</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001565394209077747</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.306869979946858e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.975183588601775e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002621250748869607</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001568829912381868</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001188555466251241</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.958780279985571e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.458494083010047e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0003293506058544105</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001161926008838539</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0008871322777087687</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.32397320937132e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.683116375432989e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003496223074231192</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001111063136098285</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0008494599734886808</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.109788666113634e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.118667203211639e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003757716954847665</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001070372684504643</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0008193232703565296</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.372187143667314e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.250891051404308e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003814106922945927</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001065286448313903</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.00081555634435506</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.798120380984561e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.447518637149318e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.000388419769246487</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001061217333851043</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0008125427371095701</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.917641949478788e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.497620989682631e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0003899775344885816</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001060708755763547</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0008121660399870828</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001009667311349105</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.56634066259973e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0003919637148169845</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001060301740044641</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.000811864653305588</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001014341960350329</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.58270478998991e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0003924056532006447</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001060250943721049</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0008118269776331824</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001021001951633238</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.603490830411219e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0003929442455638705</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001060210283230075</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0008117968682620374</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_6.xlsx
+++ b/Results/rbf_fd_parameter_study_6.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4159,4 +4160,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.097995185344746e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.428684178891437e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002022197860526604</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001018319233010213</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01001314031154404</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.781033794138007e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.656678387639802e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001678763815355958</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001029046217911</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.002944839580462678</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.092765773316263e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.810916831464957e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001780107904310623</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001039771049128335</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001552266218733871</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.44064142330636e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.085076827777442e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002059255532411508</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001050495278866433</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001061289123637199</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.798120380984561e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.447518637149318e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.000388419769246487</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001061217333851043</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0008125427371095701</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.440608191185601e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.085041033644135e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0007560471321798195</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001050490496136813</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001061284359412541</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.092728675391531e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.810876099616683e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0004651803086062271</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001039765694023383</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001552258012547274</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.781002632449962e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.656643086996792e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002957737979546056</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001029041638908342</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.002944825870539274</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.097995185344746e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.428684178891437e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002022197860526604</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001018319233010213</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01001314031154404</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>